--- a/data/trans_orig/IP38F_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP38F_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,64 +1063,64 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2927</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,64 +1406,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1525</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>975</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>975</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10222</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9073</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10535</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>86,13%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7810</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10877</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9182</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11258</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16868</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>18274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1862,107 +1862,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>18,44%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10535</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10535</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10535</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>7810</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>7810</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>7810</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>18274</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>18274</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>18274</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,64 +2092,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8247</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7392</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8612</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8247</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8247</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8247</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>7392</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>7392</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7392</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10780</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6644</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12067</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>89,34%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>55,06%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>10942</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>7879</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>13593</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>71,19%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>51,26%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>88,44%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>22138</t>
+          <t>22470</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>17904</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25159</t>
+          <t>25288</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5423</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>10,66%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>44,94%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>4428</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1777</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7491</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>28,81%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>48,74%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>12067</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>12067</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>12067</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>15370</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>15370</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>15370</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>27974</t>
+          <t>28067</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27974</t>
+          <t>28067</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27974</t>
+          <t>28067</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>37780</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>33331</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>39079</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>84,64%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>35576</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>30932</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>38048</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>77,32%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>40094</t>
+          <t>33442</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36320</t>
+          <t>29428</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41505</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,27 +2853,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>75670</t>
+          <t>71223</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70534</t>
+          <t>66462</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78726</t>
+          <t>74155</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>6049</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>15,36%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>4428</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>9072</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>22,68%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,22 +2966,22 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>39380</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>39380</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>39380</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>40004</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>40004</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>40004</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>41883</t>
+          <t>37752</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>41883</t>
+          <t>37752</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41883</t>
+          <t>37752</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>81887</t>
+          <t>77133</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81887</t>
+          <t>77133</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>81887</t>
+          <t>77133</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
